--- a/Code/2EVRPTWMM/result/Book1.xlsx
+++ b/Code/2EVRPTWMM/result/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emnormandie1-my.sharepoint.com/personal/jtang_em-normandie_fr/Documents/2EVRPMM/Code/2EVRPTWMM/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3396" documentId="8_{EFF55972-5ECA-3945-82E7-2BF28926C9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68CA5B17-96BB-D043-BB9F-4C53F7B82E8E}"/>
+  <xr:revisionPtr revIDLastSave="3397" documentId="8_{EFF55972-5ECA-3945-82E7-2BF28926C9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E1F7C4D-3699-784F-B5AC-05A613586892}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17660" activeTab="8" xr2:uid="{7D2CA5AE-647E-574D-B901-416D769C3F34}"/>
   </bookViews>
@@ -70318,7 +70318,8 @@
   <cols>
     <col min="1" max="2" width="2.83203125" customWidth="1"/>
     <col min="5" max="7" width="2.83203125" customWidth="1"/>
-    <col min="9" max="13" width="2.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
+    <col min="10" max="13" width="2.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
